--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1104 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122429363</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7039384</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122428836</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563025</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7039427</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122429582</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563079</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039427</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122429955</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563050</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122429394</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563064</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039383</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122430516</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563130</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039378</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122429982</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563021</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039514</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122429998</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562999</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039523</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122429671</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039462</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429363</v>
+        <v>122429982</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563054</v>
+        <v>563021</v>
       </c>
       <c r="R3" t="n">
-        <v>7039384</v>
+        <v>7039514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428836</v>
+        <v>122429998</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563025</v>
+        <v>562999</v>
       </c>
       <c r="R4" t="n">
-        <v>7039427</v>
+        <v>7039523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429582</v>
+        <v>122429955</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563079</v>
+        <v>563050</v>
       </c>
       <c r="R5" t="n">
-        <v>7039427</v>
+        <v>7039497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429955</v>
+        <v>122429394</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563050</v>
+        <v>563064</v>
       </c>
       <c r="R6" t="n">
-        <v>7039497</v>
+        <v>7039383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429394</v>
+        <v>122429363</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563064</v>
+        <v>563054</v>
       </c>
       <c r="R7" t="n">
-        <v>7039383</v>
+        <v>7039384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429982</v>
+        <v>122429671</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563021</v>
+        <v>563083</v>
       </c>
       <c r="R9" t="n">
-        <v>7039514</v>
+        <v>7039462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429998</v>
+        <v>122428836</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562999</v>
+        <v>563025</v>
       </c>
       <c r="R10" t="n">
-        <v>7039523</v>
+        <v>7039427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1751,19 +1751,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429671</v>
+        <v>122429582</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563083</v>
+        <v>563079</v>
       </c>
       <c r="R11" t="n">
-        <v>7039462</v>
+        <v>7039427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429982</v>
+        <v>122428836</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563021</v>
+        <v>563025</v>
       </c>
       <c r="R3" t="n">
-        <v>7039514</v>
+        <v>7039427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429998</v>
+        <v>122430516</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562999</v>
+        <v>563130</v>
       </c>
       <c r="R4" t="n">
-        <v>7039523</v>
+        <v>7039378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429955</v>
+        <v>122429394</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563050</v>
+        <v>563064</v>
       </c>
       <c r="R5" t="n">
-        <v>7039497</v>
+        <v>7039383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429394</v>
+        <v>122429982</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563064</v>
+        <v>563021</v>
       </c>
       <c r="R6" t="n">
-        <v>7039383</v>
+        <v>7039514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1278,7 +1278,7 @@
         <v>122429363</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430516</v>
+        <v>122429955</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563130</v>
+        <v>563050</v>
       </c>
       <c r="R8" t="n">
-        <v>7039378</v>
+        <v>7039497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,12 +1507,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
         <v>122429671</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428836</v>
+        <v>122429582</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563025</v>
+        <v>563079</v>
       </c>
       <c r="R10" t="n">
         <v>7039427</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1751,22 +1751,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429582</v>
+        <v>122429998</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563079</v>
+        <v>562999</v>
       </c>
       <c r="R11" t="n">
-        <v>7039427</v>
+        <v>7039523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428836</v>
+        <v>122429394</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>563064</v>
       </c>
       <c r="R3" t="n">
-        <v>7039427</v>
+        <v>7039383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429394</v>
+        <v>122429982</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563064</v>
+        <v>563021</v>
       </c>
       <c r="R5" t="n">
-        <v>7039383</v>
+        <v>7039514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429982</v>
+        <v>122429998</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563021</v>
+        <v>562999</v>
       </c>
       <c r="R6" t="n">
-        <v>7039514</v>
+        <v>7039523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429363</v>
+        <v>122429582</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563054</v>
+        <v>563079</v>
       </c>
       <c r="R7" t="n">
-        <v>7039384</v>
+        <v>7039427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429955</v>
+        <v>122428836</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563050</v>
+        <v>563025</v>
       </c>
       <c r="R8" t="n">
-        <v>7039497</v>
+        <v>7039427</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1507,19 +1507,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429671</v>
+        <v>122429363</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563083</v>
+        <v>563054</v>
       </c>
       <c r="R9" t="n">
-        <v>7039462</v>
+        <v>7039384</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429582</v>
+        <v>122429955</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563079</v>
+        <v>563050</v>
       </c>
       <c r="R10" t="n">
-        <v>7039427</v>
+        <v>7039497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429998</v>
+        <v>122429671</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562999</v>
+        <v>563083</v>
       </c>
       <c r="R11" t="n">
-        <v>7039523</v>
+        <v>7039462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429394</v>
+        <v>122429671</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -805,11 +805,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563064</v>
+        <v>563083</v>
       </c>
       <c r="R3" t="n">
-        <v>7039383</v>
+        <v>7039462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430516</v>
+        <v>122429998</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -927,11 +922,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -945,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563130</v>
+        <v>562999</v>
       </c>
       <c r="R4" t="n">
-        <v>7039378</v>
+        <v>7039523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429982</v>
+        <v>122428836</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1049,11 +1039,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1076,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563021</v>
+        <v>563025</v>
       </c>
       <c r="R5" t="n">
-        <v>7039514</v>
+        <v>7039427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1141,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429998</v>
+        <v>122429582</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1171,11 +1156,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1198,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562999</v>
+        <v>563079</v>
       </c>
       <c r="R6" t="n">
-        <v>7039523</v>
+        <v>7039427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429582</v>
+        <v>122429394</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1293,11 +1273,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1320,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563079</v>
+        <v>563064</v>
       </c>
       <c r="R7" t="n">
-        <v>7039427</v>
+        <v>7039383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122428836</v>
+        <v>122429982</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1415,11 +1390,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1442,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563025</v>
+        <v>563021</v>
       </c>
       <c r="R8" t="n">
-        <v>7039427</v>
+        <v>7039514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1507,12 +1477,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1537,11 +1507,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1641,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429955</v>
+        <v>122430516</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1659,11 +1624,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1677,7 +1637,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1686,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563050</v>
+        <v>563130</v>
       </c>
       <c r="R10" t="n">
-        <v>7039497</v>
+        <v>7039378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,12 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,19 +1711,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429671</v>
+        <v>122429955</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1781,11 +1741,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1808,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563083</v>
+        <v>563050</v>
       </c>
       <c r="R11" t="n">
-        <v>7039462</v>
+        <v>7039497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122429671</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,6 +804,11 @@
       </c>
       <c r="E3" t="n">
         <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429998</v>
+        <v>122429394</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,6 +927,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -944,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562999</v>
+        <v>563064</v>
       </c>
       <c r="R4" t="n">
-        <v>7039523</v>
+        <v>7039383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1021,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122428836</v>
+        <v>122430516</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,6 +1049,11 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1052,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563025</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7039427</v>
+        <v>7039378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429582</v>
+        <v>122429363</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,6 +1171,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1178,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563079</v>
+        <v>563054</v>
       </c>
       <c r="R6" t="n">
-        <v>7039427</v>
+        <v>7039384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1255,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429394</v>
+        <v>122428836</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,6 +1293,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1295,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563064</v>
+        <v>563025</v>
       </c>
       <c r="R7" t="n">
-        <v>7039383</v>
+        <v>7039427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1360,22 +1385,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429982</v>
+        <v>122429955</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,6 +1415,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1412,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563021</v>
+        <v>563050</v>
       </c>
       <c r="R8" t="n">
-        <v>7039514</v>
+        <v>7039497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1489,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429363</v>
+        <v>122429982</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,6 +1537,11 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1529,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563054</v>
+        <v>563021</v>
       </c>
       <c r="R9" t="n">
-        <v>7039384</v>
+        <v>7039514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1606,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430516</v>
+        <v>122429582</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,6 +1659,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1637,7 +1677,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1646,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563130</v>
+        <v>563079</v>
       </c>
       <c r="R10" t="n">
-        <v>7039378</v>
+        <v>7039427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1731,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,22 +1751,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429955</v>
+        <v>122429998</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,6 +1781,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1763,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563050</v>
+        <v>562999</v>
       </c>
       <c r="R11" t="n">
-        <v>7039497</v>
+        <v>7039523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429671</v>
+        <v>122429955</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563083</v>
+        <v>563050</v>
       </c>
       <c r="R3" t="n">
-        <v>7039462</v>
+        <v>7039497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430516</v>
+        <v>122429998</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>562999</v>
       </c>
       <c r="R5" t="n">
-        <v>7039378</v>
+        <v>7039523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,19 +1141,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429363</v>
+        <v>122430516</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1189,7 +1189,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563054</v>
+        <v>563130</v>
       </c>
       <c r="R6" t="n">
-        <v>7039384</v>
+        <v>7039378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,19 +1263,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122428836</v>
+        <v>122429671</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563025</v>
+        <v>563083</v>
       </c>
       <c r="R7" t="n">
-        <v>7039427</v>
+        <v>7039462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1385,19 +1385,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429955</v>
+        <v>122429363</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563050</v>
+        <v>563054</v>
       </c>
       <c r="R8" t="n">
-        <v>7039497</v>
+        <v>7039384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429982</v>
+        <v>122429582</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563021</v>
+        <v>563079</v>
       </c>
       <c r="R9" t="n">
-        <v>7039514</v>
+        <v>7039427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429582</v>
+        <v>122428836</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563079</v>
+        <v>563025</v>
       </c>
       <c r="R10" t="n">
         <v>7039427</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1751,19 +1751,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429998</v>
+        <v>122429982</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562999</v>
+        <v>563021</v>
       </c>
       <c r="R11" t="n">
-        <v>7039523</v>
+        <v>7039514</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429955</v>
+        <v>122429671</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563050</v>
+        <v>563083</v>
       </c>
       <c r="R3" t="n">
-        <v>7039497</v>
+        <v>7039462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429394</v>
+        <v>122429582</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563064</v>
+        <v>563079</v>
       </c>
       <c r="R4" t="n">
-        <v>7039383</v>
+        <v>7039427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429998</v>
+        <v>122429955</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562999</v>
+        <v>563050</v>
       </c>
       <c r="R5" t="n">
-        <v>7039523</v>
+        <v>7039497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430516</v>
+        <v>122429998</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1189,7 +1189,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563130</v>
+        <v>562999</v>
       </c>
       <c r="R6" t="n">
-        <v>7039378</v>
+        <v>7039523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,19 +1263,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429671</v>
+        <v>122429394</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563083</v>
+        <v>563064</v>
       </c>
       <c r="R7" t="n">
-        <v>7039462</v>
+        <v>7039383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429363</v>
+        <v>122429982</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563054</v>
+        <v>563021</v>
       </c>
       <c r="R8" t="n">
-        <v>7039384</v>
+        <v>7039514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429582</v>
+        <v>122430516</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1555,7 +1555,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563079</v>
+        <v>563130</v>
       </c>
       <c r="R9" t="n">
-        <v>7039427</v>
+        <v>7039378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,12 +1629,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429982</v>
+        <v>122429363</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563021</v>
+        <v>563054</v>
       </c>
       <c r="R11" t="n">
-        <v>7039514</v>
+        <v>7039384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429582</v>
+        <v>122428836</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563079</v>
+        <v>563025</v>
       </c>
       <c r="R4" t="n">
         <v>7039427</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,12 +1019,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429394</v>
+        <v>122429982</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563064</v>
+        <v>563021</v>
       </c>
       <c r="R7" t="n">
-        <v>7039383</v>
+        <v>7039514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429982</v>
+        <v>122429394</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563021</v>
+        <v>563064</v>
       </c>
       <c r="R8" t="n">
-        <v>7039514</v>
+        <v>7039383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122428836</v>
+        <v>122429582</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563025</v>
+        <v>563079</v>
       </c>
       <c r="R10" t="n">
         <v>7039427</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1751,12 +1751,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429671</v>
+        <v>122430516</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563083</v>
+        <v>563130</v>
       </c>
       <c r="R3" t="n">
-        <v>7039462</v>
+        <v>7039378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428836</v>
+        <v>122429671</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563025</v>
+        <v>563083</v>
       </c>
       <c r="R4" t="n">
-        <v>7039427</v>
+        <v>7039462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429955</v>
+        <v>122429982</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563050</v>
+        <v>563021</v>
       </c>
       <c r="R5" t="n">
-        <v>7039497</v>
+        <v>7039514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429998</v>
+        <v>122429955</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562999</v>
+        <v>563050</v>
       </c>
       <c r="R6" t="n">
-        <v>7039523</v>
+        <v>7039497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429982</v>
+        <v>122428836</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563021</v>
+        <v>563025</v>
       </c>
       <c r="R7" t="n">
-        <v>7039514</v>
+        <v>7039427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1385,19 +1385,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429394</v>
+        <v>122429363</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563064</v>
+        <v>563054</v>
       </c>
       <c r="R8" t="n">
-        <v>7039383</v>
+        <v>7039384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430516</v>
+        <v>122429998</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1555,7 +1555,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563130</v>
+        <v>562999</v>
       </c>
       <c r="R9" t="n">
-        <v>7039378</v>
+        <v>7039523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,19 +1629,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429582</v>
+        <v>122429394</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563079</v>
+        <v>563064</v>
       </c>
       <c r="R10" t="n">
-        <v>7039427</v>
+        <v>7039383</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429363</v>
+        <v>122429582</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563054</v>
+        <v>563079</v>
       </c>
       <c r="R11" t="n">
-        <v>7039384</v>
+        <v>7039427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430516</v>
+        <v>122428836</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563130</v>
+        <v>563025</v>
       </c>
       <c r="R3" t="n">
-        <v>7039378</v>
+        <v>7039427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
         <v>122429671</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429982</v>
+        <v>122430516</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563021</v>
+        <v>563130</v>
       </c>
       <c r="R5" t="n">
-        <v>7039514</v>
+        <v>7039378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429955</v>
+        <v>122429394</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563050</v>
+        <v>563064</v>
       </c>
       <c r="R6" t="n">
-        <v>7039497</v>
+        <v>7039383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122428836</v>
+        <v>122429582</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563025</v>
+        <v>563079</v>
       </c>
       <c r="R7" t="n">
         <v>7039427</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1385,22 +1385,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429363</v>
+        <v>122429955</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563054</v>
+        <v>563050</v>
       </c>
       <c r="R8" t="n">
-        <v>7039384</v>
+        <v>7039497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429998</v>
+        <v>122429982</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562999</v>
+        <v>563021</v>
       </c>
       <c r="R9" t="n">
-        <v>7039523</v>
+        <v>7039514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429394</v>
+        <v>122429363</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563064</v>
+        <v>563054</v>
       </c>
       <c r="R10" t="n">
-        <v>7039383</v>
+        <v>7039384</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429582</v>
+        <v>122429998</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563079</v>
+        <v>562999</v>
       </c>
       <c r="R11" t="n">
-        <v>7039427</v>
+        <v>7039523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428836</v>
+        <v>122430516</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563025</v>
+        <v>563130</v>
       </c>
       <c r="R3" t="n">
-        <v>7039427</v>
+        <v>7039378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430516</v>
+        <v>122428836</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563130</v>
+        <v>563025</v>
       </c>
       <c r="R5" t="n">
-        <v>7039378</v>
+        <v>7039427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429394</v>
+        <v>122429363</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563064</v>
+        <v>563054</v>
       </c>
       <c r="R6" t="n">
-        <v>7039383</v>
+        <v>7039384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429582</v>
+        <v>122429955</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563079</v>
+        <v>563050</v>
       </c>
       <c r="R7" t="n">
-        <v>7039427</v>
+        <v>7039497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429955</v>
+        <v>122429998</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563050</v>
+        <v>562999</v>
       </c>
       <c r="R8" t="n">
-        <v>7039497</v>
+        <v>7039523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429982</v>
+        <v>122429394</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563021</v>
+        <v>563064</v>
       </c>
       <c r="R9" t="n">
-        <v>7039514</v>
+        <v>7039383</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429363</v>
+        <v>122429582</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563054</v>
+        <v>563079</v>
       </c>
       <c r="R10" t="n">
-        <v>7039384</v>
+        <v>7039427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429998</v>
+        <v>122429982</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562999</v>
+        <v>563021</v>
       </c>
       <c r="R11" t="n">
-        <v>7039523</v>
+        <v>7039514</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 46630-2022 artfynd.xlsx
+++ b/artfynd/A 46630-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430516</v>
+        <v>122429982</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563130</v>
+        <v>563021</v>
       </c>
       <c r="R3" t="n">
-        <v>7039378</v>
+        <v>7039514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429671</v>
+        <v>122430516</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563083</v>
+        <v>563130</v>
       </c>
       <c r="R4" t="n">
-        <v>7039462</v>
+        <v>7039378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122428836</v>
+        <v>122429394</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563025</v>
+        <v>563064</v>
       </c>
       <c r="R5" t="n">
-        <v>7039427</v>
+        <v>7039383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1141,19 +1141,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429363</v>
+        <v>122428836</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563054</v>
+        <v>563025</v>
       </c>
       <c r="R6" t="n">
-        <v>7039384</v>
+        <v>7039427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1263,19 +1263,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429955</v>
+        <v>122429998</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563050</v>
+        <v>562999</v>
       </c>
       <c r="R7" t="n">
-        <v>7039497</v>
+        <v>7039523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429998</v>
+        <v>122429955</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562999</v>
+        <v>563050</v>
       </c>
       <c r="R8" t="n">
-        <v>7039523</v>
+        <v>7039497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429394</v>
+        <v>122429671</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563064</v>
+        <v>563083</v>
       </c>
       <c r="R9" t="n">
-        <v>7039383</v>
+        <v>7039462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429982</v>
+        <v>122429363</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563021</v>
+        <v>563054</v>
       </c>
       <c r="R11" t="n">
-        <v>7039514</v>
+        <v>7039384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
